--- a/ხელფასები დელივერერს.xlsx
+++ b/ხელფასები დელივერერს.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\nana\deliverer\დეკლარაცია\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kurts\OneDrive\სამუშაო დაფა\excelpdf\bank-summary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ED0CDFE-1310-49C7-9DE0-A77E7943FA1C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{766255D9-0DC5-4B46-91FF-ABC6A83EF803}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ხელფასები!#REF!</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="179021"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="62">
   <si>
     <t>თარიღი</t>
   </si>
@@ -713,23 +713,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P73"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="2" width="8.88671875" style="11"/>
-    <col min="3" max="3" width="10.6640625" style="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.6640625" style="11" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.44140625" style="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.33203125" style="11" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.88671875" style="11"/>
-    <col min="8" max="8" width="10.33203125" customWidth="1"/>
-    <col min="9" max="9" width="10.33203125" style="18" customWidth="1"/>
-    <col min="10" max="10" width="10.33203125" style="11" customWidth="1"/>
-    <col min="11" max="11" width="10.33203125" customWidth="1"/>
-    <col min="12" max="12" width="10.5546875" style="11" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.88671875" style="11" customWidth="1"/>
-    <col min="14" max="14" width="8.88671875" style="11"/>
-    <col min="15" max="16" width="10.5546875" style="11" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="8.88671875" style="11"/>
+    <col min="1" max="2" width="8.90625" style="11"/>
+    <col min="3" max="3" width="10.6328125" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.36328125" style="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.453125" style="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.36328125" style="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.90625" style="11"/>
+    <col min="8" max="8" width="10.36328125" customWidth="1"/>
+    <col min="9" max="9" width="10.36328125" style="18" customWidth="1"/>
+    <col min="10" max="10" width="10.36328125" style="11" customWidth="1"/>
+    <col min="11" max="11" width="10.36328125" customWidth="1"/>
+    <col min="12" max="12" width="10.54296875" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.90625" style="11" customWidth="1"/>
+    <col min="14" max="14" width="8.90625" style="11"/>
+    <col min="15" max="16" width="10.54296875" style="11" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="8.90625" style="11"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
@@ -755,16 +755,16 @@
     </row>
     <row r="2" spans="1:14">
       <c r="C2" s="28">
-        <v>46126</v>
+        <v>46143</v>
       </c>
       <c r="D2" s="29" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="F2" s="29">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="I2" s="15"/>
       <c r="J2" s="15"/>
@@ -774,16 +774,16 @@
     </row>
     <row r="3" spans="1:14">
       <c r="C3" s="28">
-        <v>46140</v>
+        <v>46156</v>
       </c>
       <c r="D3" s="29" t="s">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="F3" s="29">
-        <v>1200</v>
+        <v>1000</v>
       </c>
       <c r="H3" s="15"/>
       <c r="I3" s="15"/>
@@ -794,16 +794,16 @@
     </row>
     <row r="4" spans="1:14">
       <c r="C4" s="28">
-        <v>46140</v>
+        <v>46164</v>
       </c>
       <c r="D4" s="29" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="F4" s="29">
-        <v>1000</v>
+        <v>225</v>
       </c>
       <c r="H4" s="14"/>
       <c r="I4" s="15"/>
@@ -813,10 +813,18 @@
       <c r="N4" s="15"/>
     </row>
     <row r="5" spans="1:14">
-      <c r="C5" s="28"/>
-      <c r="D5" s="29"/>
-      <c r="E5" s="25"/>
-      <c r="F5" s="29"/>
+      <c r="C5" s="28">
+        <v>46170</v>
+      </c>
+      <c r="D5" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="E5" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="F5" s="29">
+        <v>1200</v>
+      </c>
       <c r="H5" s="15"/>
       <c r="I5" s="15"/>
       <c r="J5" s="26"/>
@@ -825,10 +833,18 @@
       <c r="N5" s="15"/>
     </row>
     <row r="6" spans="1:14">
-      <c r="C6" s="28"/>
-      <c r="D6" s="29"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="29"/>
+      <c r="C6" s="28">
+        <v>46170</v>
+      </c>
+      <c r="D6" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="F6" s="29">
+        <v>1000</v>
+      </c>
       <c r="I6" s="15"/>
       <c r="J6" s="21"/>
       <c r="L6" s="20"/>
@@ -836,10 +852,18 @@
       <c r="N6" s="15"/>
     </row>
     <row r="7" spans="1:14">
-      <c r="C7" s="28"/>
-      <c r="D7" s="29"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="29"/>
+      <c r="C7" s="28">
+        <v>46171</v>
+      </c>
+      <c r="D7" s="29" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="F7" s="29">
+        <v>225</v>
+      </c>
       <c r="I7" s="15"/>
       <c r="J7" s="15"/>
       <c r="L7" s="20"/>
@@ -1339,9 +1363,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:P19"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="14.5546875" customWidth="1"/>
+    <col min="2" max="2" width="14.54296875" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2049,10 +2073,10 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:P69"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="12.44140625" customWidth="1"/>
-    <col min="4" max="4" width="24.88671875" customWidth="1"/>
+    <col min="1" max="1" width="12.453125" customWidth="1"/>
+    <col min="4" max="4" width="24.90625" customWidth="1"/>
     <col min="11" max="11" width="11" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2107,19 +2131,19 @@
     <row r="2" spans="1:16">
       <c r="A2" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D2,ხელფასები!E2),map!$A$1:$P$100,2,FALSE)</f>
-        <v>01017025072</v>
+        <v>01009003935</v>
       </c>
       <c r="B2" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D2,ხელფასები!E2),map!$A$1:$P$120,3,FALSE)</f>
-        <v>ზურაბი</v>
+        <v>ალექსანდრე</v>
       </c>
       <c r="C2" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D2,ხელფასები!E2),map!$A$1:$P$120,4,FALSE)</f>
-        <v>თომაძე</v>
+        <v>ლეჟავა</v>
       </c>
       <c r="D2" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D2,ხელფასები!E2),map!$A$1:$P$102,5,FALSE)</f>
-        <v>თბილისი გიგა ლორთქიფანიძის ქ. N 13 ფ. 2</v>
+        <v>თბილისი</v>
       </c>
       <c r="E2" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D2,ხელფასები!E2),map!$A$1:$P$102,6,FALSE)</f>
@@ -2135,18 +2159,18 @@
       </c>
       <c r="H2">
         <f>IF(VLOOKUP(CONCATENATE(ხელფასები!D2,ხელფასები!E2),map!$A$1:$P$102,10,FALSE)="0",ხელფასები!F2/0.8,ხელფასები!F2/0.8/0.98)</f>
-        <v>1275.5102040816328</v>
+        <v>318.87755102040819</v>
       </c>
       <c r="I2" s="5">
         <f>IF(VLOOKUP(CONCATENATE(ხელფასები!D2,ხელფასები!E2),map!$A$1:$P$102,10,FALSE)="0","0",ხელფასები!F2/0.8/0.98*0.02)</f>
-        <v>25.510204081632654</v>
+        <v>6.3775510204081636</v>
       </c>
       <c r="J2" s="5">
         <v>0</v>
       </c>
       <c r="K2" s="4" t="str">
         <f>CONCATENATE(IF(LEN(DAY(ხელფასები!C2))&gt;1,DAY(ხელფასები!C2),CONCATENATE("0",DAY(ხელფასები!C2))),"/",MONTH(ხელფასები!C2),"/",YEAR(ხელფასები!C2))</f>
-        <v>14/4/2026</v>
+        <v>01/5/2026</v>
       </c>
       <c r="L2" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D2,ხელფასები!E2),map!$A$1:$P$102,12,FALSE)</f>
@@ -2154,7 +2178,7 @@
       </c>
       <c r="M2">
         <f>IF(VLOOKUP(CONCATENATE(ხელფასები!D2,ხელფასები!E2),map!$A$1:$P$102,10,FALSE)="0",ხელფასები!F2/0.8*0.2,(ხელფასები!F2/0.8/0.98-ხელფასები!F2/0.8/0.98*0.02)*0.2)</f>
-        <v>250</v>
+        <v>62.5</v>
       </c>
       <c r="N2" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D2,ხელფასები!E2),map!$A$1:$P$102,14,FALSE)</f>
@@ -2172,19 +2196,19 @@
     <row r="3" spans="1:16">
       <c r="A3" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D3,ხელფასები!E3),map!$A$1:$P$100,2,FALSE)</f>
-        <v>01003003707</v>
+        <v>01017025072</v>
       </c>
       <c r="B3" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D3,ხელფასები!E3),map!$A$1:$P$120,3,FALSE)</f>
-        <v>ნანა</v>
+        <v>ზურაბი</v>
       </c>
       <c r="C3" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D3,ხელფასები!E3),map!$A$1:$P$120,4,FALSE)</f>
-        <v>კურცხალია</v>
+        <v>თომაძე</v>
       </c>
       <c r="D3" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D3,ხელფასები!E3),map!$A$1:$P$102,5,FALSE)</f>
-        <v>თბილისი, მუხიანი მესამე მ/რ, კორპუსი 1</v>
+        <v>თბილისი გიგა ლორთქიფანიძის ქ. N 13 ფ. 2</v>
       </c>
       <c r="E3" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D3,ხელფასები!E3),map!$A$1:$P$102,6,FALSE)</f>
@@ -2200,18 +2224,18 @@
       </c>
       <c r="H3">
         <f>IF(VLOOKUP(CONCATENATE(ხელფასები!D3,ხელფასები!E3),map!$A$1:$P$102,10,FALSE)="0",ხელფასები!F3/0.8,ხელფასები!F3/0.8/0.98)</f>
-        <v>1530.6122448979593</v>
+        <v>1275.5102040816328</v>
       </c>
       <c r="I3" s="5">
         <f>IF(VLOOKUP(CONCATENATE(ხელფასები!D3,ხელფასები!E3),map!$A$1:$P$102,10,FALSE)="0","0",ხელფასები!F3/0.8/0.98*0.02)</f>
-        <v>30.612244897959187</v>
+        <v>25.510204081632654</v>
       </c>
       <c r="J3" s="5">
         <v>0</v>
       </c>
       <c r="K3" s="4" t="str">
         <f>CONCATENATE(IF(LEN(DAY(ხელფასები!C3))&gt;1,DAY(ხელფასები!C3),CONCATENATE("0",DAY(ხელფასები!C3))),"/",MONTH(ხელფასები!C3),"/",YEAR(ხელფასები!C3))</f>
-        <v>28/4/2026</v>
+        <v>14/5/2026</v>
       </c>
       <c r="L3" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D3,ხელფასები!E3),map!$A$1:$P$102,12,FALSE)</f>
@@ -2219,7 +2243,7 @@
       </c>
       <c r="M3">
         <f>IF(VLOOKUP(CONCATENATE(ხელფასები!D3,ხელფასები!E3),map!$A$1:$P$102,10,FALSE)="0",ხელფასები!F3/0.8*0.2,(ხელფასები!F3/0.8/0.98-ხელფასები!F3/0.8/0.98*0.02)*0.2)</f>
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="N3" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D3,ხელფასები!E3),map!$A$1:$P$102,14,FALSE)</f>
@@ -2237,19 +2261,19 @@
     <row r="4" spans="1:16">
       <c r="A4" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D4,ხელფასები!E4),map!$A$1:$P$100,2,FALSE)</f>
-        <v>01017025072</v>
+        <v>01009003935</v>
       </c>
       <c r="B4" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D4,ხელფასები!E4),map!$A$1:$P$120,3,FALSE)</f>
-        <v>ზურაბი</v>
+        <v>ალექსანდრე</v>
       </c>
       <c r="C4" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D4,ხელფასები!E4),map!$A$1:$P$120,4,FALSE)</f>
-        <v>თომაძე</v>
+        <v>ლეჟავა</v>
       </c>
       <c r="D4" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D4,ხელფასები!E4),map!$A$1:$P$102,5,FALSE)</f>
-        <v>თბილისი გიგა ლორთქიფანიძის ქ. N 13 ფ. 2</v>
+        <v>თბილისი</v>
       </c>
       <c r="E4" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D4,ხელფასები!E4),map!$A$1:$P$102,6,FALSE)</f>
@@ -2265,18 +2289,18 @@
       </c>
       <c r="H4">
         <f>IF(VLOOKUP(CONCATENATE(ხელფასები!D4,ხელფასები!E4),map!$A$1:$P$102,10,FALSE)="0",ხელფასები!F4/0.8,ხელფასები!F4/0.8/0.98)</f>
-        <v>1275.5102040816328</v>
+        <v>286.98979591836735</v>
       </c>
       <c r="I4" s="5">
         <f>IF(VLOOKUP(CONCATENATE(ხელფასები!D4,ხელფასები!E4),map!$A$1:$P$102,10,FALSE)="0","0",ხელფასები!F4/0.8/0.98*0.02)</f>
-        <v>25.510204081632654</v>
+        <v>5.7397959183673475</v>
       </c>
       <c r="J4" s="5">
         <v>0</v>
       </c>
       <c r="K4" s="4" t="str">
         <f>CONCATENATE(IF(LEN(DAY(ხელფასები!C4))&gt;1,DAY(ხელფასები!C4),CONCATENATE("0",DAY(ხელფასები!C4))),"/",MONTH(ხელფასები!C4),"/",YEAR(ხელფასები!C4))</f>
-        <v>28/4/2026</v>
+        <v>22/5/2026</v>
       </c>
       <c r="L4" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D4,ხელფასები!E4),map!$A$1:$P$102,12,FALSE)</f>
@@ -2284,7 +2308,7 @@
       </c>
       <c r="M4">
         <f>IF(VLOOKUP(CONCATENATE(ხელფასები!D4,ხელფასები!E4),map!$A$1:$P$102,10,FALSE)="0",ხელფასები!F4/0.8*0.2,(ხელფასები!F4/0.8/0.98-ხელფასები!F4/0.8/0.98*0.02)*0.2)</f>
-        <v>250</v>
+        <v>56.25</v>
       </c>
       <c r="N4" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D4,ხელფასები!E4),map!$A$1:$P$102,14,FALSE)</f>
@@ -2300,196 +2324,196 @@
       </c>
     </row>
     <row r="5" spans="1:16">
-      <c r="A5">
+      <c r="A5" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D5,ხელფასები!E5),map!$A$1:$P$100,2,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="B5">
+        <v>01003003707</v>
+      </c>
+      <c r="B5" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D5,ხელფასები!E5),map!$A$1:$P$120,3,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="C5">
+        <v>ნანა</v>
+      </c>
+      <c r="C5" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D5,ხელფასები!E5),map!$A$1:$P$120,4,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D5">
+        <v>კურცხალია</v>
+      </c>
+      <c r="D5" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D5,ხელფასები!E5),map!$A$1:$P$102,5,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="E5">
+        <v>თბილისი, მუხიანი მესამე მ/რ, კორპუსი 1</v>
+      </c>
+      <c r="E5" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D5,ხელფასები!E5),map!$A$1:$P$102,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F5">
+        <v>268</v>
+      </c>
+      <c r="F5" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D5,ხელფასები!E5),map!$A$1:$P$102,7,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="G5">
+        <v>4</v>
+      </c>
+      <c r="G5" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D5,ხელფასები!E5),map!$A$1:$P$102,8,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5">
         <f>IF(VLOOKUP(CONCATENATE(ხელფასები!D5,ხელფასები!E5),map!$A$1:$P$102,10,FALSE)="0",ხელფასები!F5/0.8,ხელფასები!F5/0.8/0.98)</f>
-        <v>0</v>
+        <v>1530.6122448979593</v>
       </c>
       <c r="I5" s="5">
         <f>IF(VLOOKUP(CONCATENATE(ხელფასები!D5,ხელფასები!E5),map!$A$1:$P$102,10,FALSE)="0","0",ხელფასები!F5/0.8/0.98*0.02)</f>
-        <v>0</v>
+        <v>30.612244897959187</v>
       </c>
       <c r="J5" s="5">
         <v>0</v>
       </c>
       <c r="K5" s="4" t="str">
         <f>CONCATENATE(IF(LEN(DAY(ხელფასები!C5))&gt;1,DAY(ხელფასები!C5),CONCATENATE("0",DAY(ხელფასები!C5))),"/",MONTH(ხელფასები!C5),"/",YEAR(ხელფასები!C5))</f>
-        <v>00/1/1900</v>
-      </c>
-      <c r="L5">
+        <v>28/5/2026</v>
+      </c>
+      <c r="L5" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D5,ხელფასები!E5),map!$A$1:$P$102,12,FALSE)</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M5">
         <f>IF(VLOOKUP(CONCATENATE(ხელფასები!D5,ხელფასები!E5),map!$A$1:$P$102,10,FALSE)="0",ხელფასები!F5/0.8*0.2,(ხელფასები!F5/0.8/0.98-ხელფასები!F5/0.8/0.98*0.02)*0.2)</f>
-        <v>0</v>
-      </c>
-      <c r="N5">
+        <v>300</v>
+      </c>
+      <c r="N5" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D5,ხელფასები!E5),map!$A$1:$P$102,14,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="O5">
+      <c r="O5" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D5,ხელფასები!E5),map!$A$1:$P$102,15,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="P5">
+      <c r="P5" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D5,ხელფასები!E5),map!$A$1:$P$102,16,FALSE)</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:16">
-      <c r="A6">
+      <c r="A6" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D6,ხელფასები!E6),map!$A$1:$P$100,2,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="B6">
+        <v>01017025072</v>
+      </c>
+      <c r="B6" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D6,ხელფასები!E6),map!$A$1:$P$120,3,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="C6">
+        <v>ზურაბი</v>
+      </c>
+      <c r="C6" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D6,ხელფასები!E6),map!$A$1:$P$120,4,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D6">
+        <v>თომაძე</v>
+      </c>
+      <c r="D6" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D6,ხელფასები!E6),map!$A$1:$P$102,5,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="E6">
+        <v>თბილისი გიგა ლორთქიფანიძის ქ. N 13 ფ. 2</v>
+      </c>
+      <c r="E6" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D6,ხელფასები!E6),map!$A$1:$P$102,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F6">
+        <v>268</v>
+      </c>
+      <c r="F6" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D6,ხელფასები!E6),map!$A$1:$P$102,7,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="G6">
+        <v>4</v>
+      </c>
+      <c r="G6" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D6,ხელფასები!E6),map!$A$1:$P$102,8,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6">
         <f>IF(VLOOKUP(CONCATENATE(ხელფასები!D6,ხელფასები!E6),map!$A$1:$P$102,10,FALSE)="0",ხელფასები!F6/0.8,ხელფასები!F6/0.8/0.98)</f>
-        <v>0</v>
+        <v>1275.5102040816328</v>
       </c>
       <c r="I6" s="5">
         <f>IF(VLOOKUP(CONCATENATE(ხელფასები!D6,ხელფასები!E6),map!$A$1:$P$102,10,FALSE)="0","0",ხელფასები!F6/0.8/0.98*0.02)</f>
-        <v>0</v>
+        <v>25.510204081632654</v>
       </c>
       <c r="J6" s="5">
         <v>0</v>
       </c>
       <c r="K6" s="4" t="str">
         <f>CONCATENATE(IF(LEN(DAY(ხელფასები!C6))&gt;1,DAY(ხელფასები!C6),CONCATENATE("0",DAY(ხელფასები!C6))),"/",MONTH(ხელფასები!C6),"/",YEAR(ხელფასები!C6))</f>
-        <v>00/1/1900</v>
-      </c>
-      <c r="L6">
+        <v>28/5/2026</v>
+      </c>
+      <c r="L6" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D6,ხელფასები!E6),map!$A$1:$P$102,12,FALSE)</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M6">
         <f>IF(VLOOKUP(CONCATENATE(ხელფასები!D6,ხელფასები!E6),map!$A$1:$P$102,10,FALSE)="0",ხელფასები!F6/0.8*0.2,(ხელფასები!F6/0.8/0.98-ხელფასები!F6/0.8/0.98*0.02)*0.2)</f>
-        <v>0</v>
-      </c>
-      <c r="N6">
+        <v>250</v>
+      </c>
+      <c r="N6" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D6,ხელფასები!E6),map!$A$1:$P$102,14,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="O6">
+      <c r="O6" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D6,ხელფასები!E6),map!$A$1:$P$102,15,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="P6">
+      <c r="P6" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D6,ხელფასები!E6),map!$A$1:$P$102,16,FALSE)</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:16">
-      <c r="A7">
+      <c r="A7" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D7,ხელფასები!E7),map!$A$1:$P$100,2,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="B7">
+        <v>01009003935</v>
+      </c>
+      <c r="B7" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D7,ხელფასები!E7),map!$A$1:$P$120,3,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="C7">
+        <v>ალექსანდრე</v>
+      </c>
+      <c r="C7" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D7,ხელფასები!E7),map!$A$1:$P$120,4,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D7">
+        <v>ლეჟავა</v>
+      </c>
+      <c r="D7" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D7,ხელფასები!E7),map!$A$1:$P$102,5,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="E7">
+        <v>თბილისი</v>
+      </c>
+      <c r="E7" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D7,ხელფასები!E7),map!$A$1:$P$102,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F7">
+        <v>268</v>
+      </c>
+      <c r="F7" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D7,ხელფასები!E7),map!$A$1:$P$102,7,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="G7">
+        <v>4</v>
+      </c>
+      <c r="G7" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D7,ხელფასები!E7),map!$A$1:$P$102,8,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7">
         <f>IF(VLOOKUP(CONCATENATE(ხელფასები!D7,ხელფასები!E7),map!$A$1:$P$102,10,FALSE)="0",ხელფასები!F7/0.8,ხელფასები!F7/0.8/0.98)</f>
-        <v>0</v>
+        <v>286.98979591836735</v>
       </c>
       <c r="I7" s="5">
         <f>IF(VLOOKUP(CONCATENATE(ხელფასები!D7,ხელფასები!E7),map!$A$1:$P$102,10,FALSE)="0","0",ხელფასები!F7/0.8/0.98*0.02)</f>
-        <v>0</v>
+        <v>5.7397959183673475</v>
       </c>
       <c r="J7" s="5">
         <v>0</v>
       </c>
       <c r="K7" s="4" t="str">
         <f>CONCATENATE(IF(LEN(DAY(ხელფასები!C7))&gt;1,DAY(ხელფასები!C7),CONCATENATE("0",DAY(ხელფასები!C7))),"/",MONTH(ხელფასები!C7),"/",YEAR(ხელფასები!C7))</f>
-        <v>00/1/1900</v>
-      </c>
-      <c r="L7">
+        <v>29/5/2026</v>
+      </c>
+      <c r="L7" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D7,ხელფასები!E7),map!$A$1:$P$102,12,FALSE)</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M7">
         <f>IF(VLOOKUP(CONCATENATE(ხელფასები!D7,ხელფასები!E7),map!$A$1:$P$102,10,FALSE)="0",ხელფასები!F7/0.8*0.2,(ხელფასები!F7/0.8/0.98-ხელფასები!F7/0.8/0.98*0.02)*0.2)</f>
-        <v>0</v>
-      </c>
-      <c r="N7">
+        <v>56.25</v>
+      </c>
+      <c r="N7" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D7,ხელფასები!E7),map!$A$1:$P$102,14,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="O7">
+      <c r="O7" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D7,ხელფასები!E7),map!$A$1:$P$102,15,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="P7">
+      <c r="P7" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D7,ხელფასები!E7),map!$A$1:$P$102,16,FALSE)</f>
         <v>0</v>
       </c>
@@ -6532,7 +6556,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
@@ -6567,7 +6591,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:E12"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="3" max="4" width="12" bestFit="1" customWidth="1"/>
   </cols>
